--- a/business_forms/032_project_enquiry_form--business_forms.xlsx
+++ b/business_forms/032_project_enquiry_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>project_enquiry_form</t>
+          <t>Project Enquiry Form</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>company_name</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Project Description</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>description_of_project</t>
+          <t>Description of Project</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>deadline</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,128 +686,105 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>project_enquiry_form_type</t>
+          <t>Project Type</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>timeline</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Timeline</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>deadline</t>
+          <t>budget</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>deadline</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>deadline</t>
+          <t>project_manager</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>deadline</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>deadline</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>deadline</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -822,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option a</t>
         </is>
       </c>
     </row>
@@ -872,46 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>name_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>option2</t>
+          <t>option b</t>
         </is>
       </c>
     </row>
